--- a/data/trans_orig/P6901-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6901-Clase-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29343</t>
+          <t>29526</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45671</t>
+          <t>45222</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21025</t>
+          <t>21500</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34267</t>
+          <t>34426</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54417</t>
+          <t>54778</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76888</t>
+          <t>77023</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,94%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19412</t>
+          <t>19861</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35740</t>
+          <t>35557</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12383</t>
+          <t>12224</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25625</t>
+          <t>25150</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34845</t>
+          <t>34710</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57316</t>
+          <t>56955</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>50,97%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14395</t>
+          <t>15226</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28274</t>
+          <t>28655</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29979</t>
+          <t>30109</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39599</t>
+          <t>38768</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47256</t>
+          <t>47743</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64454</t>
+          <t>65293</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>77,76%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14081</t>
+          <t>13700</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27960</t>
+          <t>27129</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11637</t>
+          <t>11507</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19516</t>
+          <t>18677</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36714</t>
+          <t>36227</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,14%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71518</t>
+          <t>70861</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87082</t>
+          <t>86676</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>8689</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15320</t>
+          <t>15302</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83927</t>
+          <t>83447</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100931</t>
+          <t>100868</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,72%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12948</t>
+          <t>13354</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28512</t>
+          <t>29169</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>985</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7382</t>
+          <t>7598</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15385</t>
+          <t>15448</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32389</t>
+          <t>32869</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,26%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>148039</t>
+          <t>148687</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>170276</t>
+          <t>171588</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29088</t>
+          <t>28941</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41680</t>
+          <t>41796</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>184999</t>
+          <t>182705</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>211028</t>
+          <t>208512</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>83,15%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30553</t>
+          <t>29241</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52790</t>
+          <t>52142</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20858</t>
+          <t>21005</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39747</t>
+          <t>42263</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65776</t>
+          <t>68070</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>27,14%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47296</t>
+          <t>46732</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59269</t>
+          <t>58966</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52796</t>
+          <t>53096</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62775</t>
+          <t>62689</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>104104</t>
+          <t>104079</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>119915</t>
+          <t>119934</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16713</t>
+          <t>17277</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12827</t>
+          <t>12527</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9717</t>
+          <t>9698</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25528</t>
+          <t>25553</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2438,107 +2438,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>334</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>354578</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>335509</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>372213</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>167</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>171575</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>158264</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>183829</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>501</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>526154</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>501537</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>546815</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,97%</t>
         </is>
       </c>
     </row>
@@ -2551,107 +2551,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>116</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>117727</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100092</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>136796</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>48546</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36292</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>61857</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>164</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166273</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>145612</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>190890</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -2664,462 +2664,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472305</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472305</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472305</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>215</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220121</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220121</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220121</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>665</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>354578</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>334550</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>372165</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>75,07%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>70,83%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>78,8%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>171575</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>158216</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>182869</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>77,95%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>71,88%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>83,08%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>526154</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>501482</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>549421</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>75,99%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>72,42%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>79,35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>117727</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>100140</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>137755</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>24,93%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>21,2%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>29,17%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>48546</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>37252</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>61905</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>22,05%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>16,92%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>28,12%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>166273</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>143006</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>190945</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>24,01%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>20,65%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>27,58%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>472305</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>472305</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>472305</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>220121</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>220121</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>220121</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>692427</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>692427</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>692427</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -3129,7 +2786,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3142,7 +2798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3173,7 +2829,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2012 (tasa de respuesta: 98,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3024,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27562</t>
+          <t>28404</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42238</t>
+          <t>43495</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3039,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3059,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17993</t>
+          <t>18405</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31048</t>
+          <t>31352</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3074,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3094,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>49545</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69770</t>
+          <t>69933</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3109,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,98%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3137,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13220</t>
+          <t>11963</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27896</t>
+          <t>27054</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3152,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3172,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10654</t>
+          <t>10350</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23709</t>
+          <t>23297</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3187,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3207,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27390</t>
+          <t>27227</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47253</t>
+          <t>47615</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3222,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>49,01%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3367,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20659</t>
+          <t>21561</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31843</t>
+          <t>32347</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3382,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3402,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14197</t>
+          <t>13392</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24331</t>
+          <t>24415</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3417,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3437,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38784</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54026</t>
+          <t>53571</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3452,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,09%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3480,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15683</t>
+          <t>14781</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3495,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3515,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12417</t>
+          <t>13222</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3530,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3550,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8930</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24172</t>
+          <t>24310</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3565,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,61%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +3710,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48060</t>
+          <t>47610</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63582</t>
+          <t>63862</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +3725,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +3745,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25971</t>
+          <t>25580</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32756</t>
+          <t>32741</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +3760,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +3780,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76453</t>
+          <t>76870</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94459</t>
+          <t>95491</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +3795,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>84,41%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +3823,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15823</t>
+          <t>15543</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31345</t>
+          <t>31795</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +3838,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +3858,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>981</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7751</t>
+          <t>8142</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +3873,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +3893,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18667</t>
+          <t>17635</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36673</t>
+          <t>36256</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +3908,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4053,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80335</t>
+          <t>78990</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98317</t>
+          <t>97244</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4068,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4088,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48868</t>
+          <t>48256</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61065</t>
+          <t>61097</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4103,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4123,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>133053</t>
+          <t>133023</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>154444</t>
+          <t>155397</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4138,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>84,32%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4166,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18027</t>
+          <t>19100</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36009</t>
+          <t>37354</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4181,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4201,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19087</t>
+          <t>19699</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4216,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4236,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29855</t>
+          <t>28902</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51246</t>
+          <t>51276</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4251,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4396,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28452</t>
+          <t>28243</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37914</t>
+          <t>37828</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4411,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4431,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29070</t>
+          <t>28500</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39913</t>
+          <t>40008</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4446,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4466,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62374</t>
+          <t>61677</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76524</t>
+          <t>76017</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4481,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>90,85%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4509,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11552</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4524,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4544,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14598</t>
+          <t>15168</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4559,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4579,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7148</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21298</t>
+          <t>21995</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4594,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +4719,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5073,107 +4729,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>234</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>243376</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>227282</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>259495</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>152</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166663</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>153048</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>177544</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>386</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>410038</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>388400</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>429377</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,34%</t>
         </is>
       </c>
     </row>
@@ -5186,107 +4842,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84178</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>68059</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100272</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46998</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36117</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>60613</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>124</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>131176</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>111837</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>152814</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -5299,462 +4955,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>314</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>327554</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>327554</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>327554</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>196</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>213661</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>213661</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>213661</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>510</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>541214</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>541214</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>541214</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>243376</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>226963</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>260196</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>74,3%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>69,29%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>79,44%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>166663</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>153383</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>178952</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>78,0%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>71,79%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>83,76%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>386</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>410038</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>389548</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>431185</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>75,76%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>71,98%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>79,67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>84178</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>67358</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>100591</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>25,7%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>20,56%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>30,71%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>46998</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>34709</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>60278</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>22,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>16,24%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>28,21%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>131176</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>110029</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>151666</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>24,24%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>20,33%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>28,02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>327554</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>327554</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>327554</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>213661</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>213661</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>213661</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>541214</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>541214</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>541214</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -5764,7 +5077,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5777,7 +5089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5808,7 +5120,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +5315,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18021</t>
+          <t>18221</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32915</t>
+          <t>32012</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +5330,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +5350,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21021</t>
+          <t>22208</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34851</t>
+          <t>34508</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +5365,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +5385,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43918</t>
+          <t>43119</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63618</t>
+          <t>63811</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +5400,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,73%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +5428,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13996</t>
+          <t>14899</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28890</t>
+          <t>28690</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +5443,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +5463,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11083</t>
+          <t>11426</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24913</t>
+          <t>23726</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +5478,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +5498,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29227</t>
+          <t>29034</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48927</t>
+          <t>49726</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +5513,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>53,56%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +5658,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17808</t>
+          <t>18095</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27144</t>
+          <t>27116</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +5673,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +5693,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21858</t>
+          <t>21906</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28496</t>
+          <t>28506</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +5708,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +5728,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43397</t>
+          <t>43518</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54692</t>
+          <t>54527</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +5743,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +5771,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12428</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +5786,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +5806,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>888</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7536</t>
+          <t>7488</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +5821,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +5841,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16234</t>
+          <t>16113</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +5856,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6001,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37462</t>
+          <t>37290</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53756</t>
+          <t>53024</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6016,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,7 +6036,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -6739,7 +6051,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -6759,12 +6071,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45064</t>
+          <t>45343</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62369</t>
+          <t>62208</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6086,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,36%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6114,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>13866</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29428</t>
+          <t>29600</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6129,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6842,7 +6154,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6857,7 +6169,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6184,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14090</t>
+          <t>14251</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31395</t>
+          <t>31116</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6199,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,7%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +6344,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97295</t>
+          <t>97694</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>117078</t>
+          <t>116712</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +6359,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +6379,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68669</t>
+          <t>69178</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81353</t>
+          <t>80919</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +6394,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +6414,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>173038</t>
+          <t>173164</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>195496</t>
+          <t>195287</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +6429,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,39%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +6457,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19791</t>
+          <t>20157</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39574</t>
+          <t>39175</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +6472,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +6492,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15408</t>
+          <t>14899</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +6507,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +6527,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25450</t>
+          <t>25659</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47908</t>
+          <t>47782</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +6542,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +6687,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50725</t>
+          <t>50628</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63050</t>
+          <t>63545</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +6702,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +6722,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38184</t>
+          <t>38340</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46252</t>
+          <t>46277</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +6737,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +6757,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92165</t>
+          <t>92551</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107420</t>
+          <t>108097</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +6772,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,85%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +6800,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18370</t>
+          <t>18467</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +6815,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +6835,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9140</t>
+          <t>8984</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +6850,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +6870,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8999</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24254</t>
+          <t>23868</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +6885,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7010,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7708,107 +7020,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>241</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>260795</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>242826</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>274945</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>176</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>183756</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>172284</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>193490</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>417</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>444551</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>422810</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>463700</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,88%</t>
         </is>
       </c>
     </row>
@@ -7821,107 +7133,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>89206</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75056</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>107175</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32542</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22808</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>44014</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>112</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>121748</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>102599</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>143489</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,34%</t>
         </is>
       </c>
     </row>
@@ -7934,462 +7246,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>322</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350001</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350001</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350001</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>207</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216298</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216298</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216298</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>529</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566299</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566299</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566299</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>260795</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>243733</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>277615</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>74,51%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>69,64%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>79,32%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>183756</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>171011</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>192299</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>84,96%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>79,06%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>88,9%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>444551</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>423295</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>464402</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>78,5%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>74,75%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>82,01%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>89206</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>72386</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>106268</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>25,49%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>20,68%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>30,36%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>32542</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>23999</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>45287</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>15,04%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>11,1%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>20,94%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>121748</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>101897</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>143004</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>21,5%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>17,99%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>25,25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>350001</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>350001</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>350001</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>216298</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>216298</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>216298</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>529</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>566299</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>566299</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>566299</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -8399,7 +7368,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8412,7 +7380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8443,7 +7411,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +7606,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14314</t>
+          <t>14738</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27983</t>
+          <t>27805</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +7621,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +7641,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30438</t>
+          <t>30668</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42995</t>
+          <t>42800</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +7656,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +7676,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49484</t>
+          <t>47860</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67464</t>
+          <t>67602</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +7691,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,32%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +7719,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17833</t>
+          <t>18011</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31502</t>
+          <t>31078</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +7734,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +7754,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16295</t>
+          <t>16490</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28852</t>
+          <t>28622</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +7769,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +7789,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37642</t>
+          <t>37504</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55622</t>
+          <t>57246</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +7804,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>54,47%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +7949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20731</t>
+          <t>21609</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35696</t>
+          <t>35634</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +7964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +7984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17235</t>
+          <t>17087</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29223</t>
+          <t>29507</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +7999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +8019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42518</t>
+          <t>41893</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62231</t>
+          <t>61646</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +8034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>66,33%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +8062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15083</t>
+          <t>15145</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30048</t>
+          <t>29170</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +8077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +8097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12935</t>
+          <t>12651</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24923</t>
+          <t>25071</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +8112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +8132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30706</t>
+          <t>31291</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>50419</t>
+          <t>51044</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +8147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,92%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +8292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32941</t>
+          <t>32337</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47634</t>
+          <t>47190</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +8307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +8327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11084</t>
+          <t>10947</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16624</t>
+          <t>16634</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +8342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +8362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46534</t>
+          <t>45904</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62466</t>
+          <t>62129</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +8377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,36%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +8405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10889</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25582</t>
+          <t>26186</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +8420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +8440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +8455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +8475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13896</t>
+          <t>14233</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29828</t>
+          <t>30458</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +8490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,89%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +8635,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100638</t>
+          <t>100230</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118465</t>
+          <t>118437</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +8650,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +8670,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75486</t>
+          <t>75406</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91364</t>
+          <t>90585</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +8685,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +8705,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>183586</t>
+          <t>183738</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>205976</t>
+          <t>205959</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +8720,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,18%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +8748,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14753</t>
+          <t>14781</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32580</t>
+          <t>32988</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +8763,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +8783,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14394</t>
+          <t>15173</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30272</t>
+          <t>30352</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +8798,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +8818,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33000</t>
+          <t>33017</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55390</t>
+          <t>55238</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +8833,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +8978,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38029</t>
+          <t>37687</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49328</t>
+          <t>49179</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +8993,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +9013,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>97008</t>
+          <t>99417</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>124087</t>
+          <t>123859</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +9028,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +9048,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>143260</t>
+          <t>142634</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>171244</t>
+          <t>170505</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +9063,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +9091,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13141</t>
+          <t>13483</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +9106,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +9126,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30239</t>
+          <t>27830</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +9141,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +9161,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7172</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35156</t>
+          <t>35782</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +9176,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -10333,7 +9301,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10343,107 +9311,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>248</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>229067</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>262543</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>373</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>275728</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>257515</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>297636</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>621</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>522705</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>495623</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>551911</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,78%</t>
         </is>
       </c>
     </row>
@@ -10456,107 +9424,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>92528</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>76962</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>110438</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>98</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>76564</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54656</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>94777</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>188</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>169092</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>139886</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>196174</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,36%</t>
         </is>
       </c>
     </row>
@@ -10569,462 +9537,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>338</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339505</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339505</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339505</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>471</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352292</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352292</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352292</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>809</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>691797</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>691797</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>691797</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>246977</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>229201</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>264426</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>72,75%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>67,51%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>77,89%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>275728</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>255683</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>296872</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>78,27%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>72,58%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>84,27%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>522705</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>496619</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>552093</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>75,56%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>71,79%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>79,81%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>92528</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>75079</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>110304</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>27,25%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>22,11%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>32,49%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>76564</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>55420</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>96609</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>21,73%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>15,73%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>27,42%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>169092</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>139704</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>195178</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>24,44%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>20,19%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>28,21%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>339505</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>339505</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>339505</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>352292</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>352292</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>352292</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>809</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>691797</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>691797</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>691797</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -11034,7 +9659,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
